--- a/data/trans_orig/P6903-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6903-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23202</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18972</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36250</t>
+          <t>36238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41881</t>
+          <t>41371</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55467</t>
+          <t>55351</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29368</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40494</t>
+          <t>40360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75483</t>
+          <t>75495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92761</t>
+          <t>93175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>13194</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25290</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>26521</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37421</t>
+          <t>37730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27835</t>
+          <t>28422</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38296</t>
+          <t>38376</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58680</t>
+          <t>58710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73824</t>
+          <t>73428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26981</t>
+          <t>26191</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46945</t>
+          <t>47430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31111</t>
+          <t>30075</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53975</t>
+          <t>51545</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53085</t>
+          <t>52600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73049</t>
+          <t>73839</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62341</t>
+          <t>64771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85205</t>
+          <t>86241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>74,14%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52535</t>
+          <t>52569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80452</t>
+          <t>78832</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23110</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67998</t>
+          <t>66663</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97118</t>
+          <t>95716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120377</t>
+          <t>121997</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148294</t>
+          <t>148260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26836</t>
+          <t>27360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39955</t>
+          <t>40075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153657</t>
+          <t>155059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182777</t>
+          <t>184112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,42%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>30454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20491</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36792</t>
+          <t>36680</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>39611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63076</t>
+          <t>63236</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33193</t>
+          <t>33555</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49223</t>
+          <t>49465</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>28943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45132</t>
+          <t>44883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66556</t>
+          <t>66396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90120</t>
+          <t>90021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2438,107 +2438,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149217</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129613</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67753</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54919</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81376</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216970</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>192104</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>242897</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -2551,107 +2551,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>311</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>323088</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301622</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>342692</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152368</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138745</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165202</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>460</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>475457</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>449530</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>500323</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -2664,462 +2664,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>149217</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>128890</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>170546</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>31,59%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>27,29%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>36,11%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>67753</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>55237</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>83314</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>30,78%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>25,09%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>37,85%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>216970</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>192224</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>242444</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>31,33%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>27,76%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>35,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>323088</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>301759</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>343415</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>68,41%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>63,89%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>72,71%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>152368</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>136807</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>164884</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>69,22%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>62,15%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>74,91%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>475457</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>449983</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>500203</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>68,67%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>64,99%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>72,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3129,7 +2786,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3142,7 +2798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3173,7 +2829,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2012 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3024,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19297</t>
+          <t>19277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3039,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3059,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17732</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3074,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3094,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33393</t>
+          <t>32395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3109,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3137,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36161</t>
+          <t>36181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48892</t>
+          <t>48648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3152,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3172,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26137</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37741</t>
+          <t>38518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3187,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3207,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65935</t>
+          <t>66933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84022</t>
+          <t>84476</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3222,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3367,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3382,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3402,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>914</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3417,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3437,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>20778</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3452,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3480,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>20645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31208</t>
+          <t>31337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3495,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3515,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17483</t>
+          <t>18271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25708</t>
+          <t>25700</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3530,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3550,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42911</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55211</t>
+          <t>54958</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3565,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,3%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +3710,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>25008</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +3725,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +3745,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19159</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +3760,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +3780,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>21620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42009</t>
+          <t>41152</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +3795,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +3823,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52485</t>
+          <t>53334</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67468</t>
+          <t>67973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +3838,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +3858,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14563</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26486</t>
+          <t>26227</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +3873,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +3893,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70054</t>
+          <t>70911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89462</t>
+          <t>90443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +3908,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4053,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17438</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35355</t>
+          <t>36453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4068,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4088,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19758</t>
+          <t>19645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36535</t>
+          <t>36119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4103,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4123,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42238</t>
+          <t>41713</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66887</t>
+          <t>67508</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4138,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4166,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78802</t>
+          <t>77704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96719</t>
+          <t>96908</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4181,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4201,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>30686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47047</t>
+          <t>47160</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4216,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4236,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114075</t>
+          <t>113454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138724</t>
+          <t>139249</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4251,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4396,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18508</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4411,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4431,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26057</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4446,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4466,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22206</t>
+          <t>22525</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40306</t>
+          <t>41355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4481,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>49,43%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4509,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21496</t>
+          <t>21296</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33157</t>
+          <t>33027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4524,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4544,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31373</t>
+          <t>31784</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4559,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4579,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43366</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61466</t>
+          <t>61147</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4594,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +4719,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5073,107 +4729,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>77275</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63279</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74473</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>61476</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88549</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>142</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>151748</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129351</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>175264</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -5186,107 +4842,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>247028</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>230438</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>261024</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>128</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140205</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153202</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>366</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387233</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>363717</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>409630</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -5299,462 +4955,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>311</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324303</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324303</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324303</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>197</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214678</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214678</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214678</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>508</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>538981</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>538981</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>538981</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>77275</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>62308</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>92651</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>23,83%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>28,57%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>74473</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>61107</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>89027</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>34,69%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>28,46%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>151748</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>132031</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>174382</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>24,5%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>32,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>247028</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>231652</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>261995</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>76,17%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>71,43%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>80,79%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>140205</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>125651</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>153571</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>65,31%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>58,53%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>71,54%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>387233</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>364599</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>406950</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>71,85%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>67,65%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>75,5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>324303</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>324303</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>324303</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>214678</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>214678</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>214678</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>538981</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>538981</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>538981</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5764,7 +5077,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5777,7 +5089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5808,7 +5120,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +5315,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23679</t>
+          <t>23651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +5330,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +5350,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28700</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +5365,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +5385,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28886</t>
+          <t>28028</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48409</t>
+          <t>48194</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +5400,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +5428,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>23260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37282</t>
+          <t>37538</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +5443,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +5463,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>17431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31363</t>
+          <t>31522</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +5478,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +5498,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44436</t>
+          <t>44651</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63959</t>
+          <t>64817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +5513,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +5658,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +5673,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +5693,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +5708,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +5728,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14729</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29893</t>
+          <t>29991</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +5743,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,29%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +5771,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23269</t>
+          <t>23122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +5786,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +5806,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14296</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23926</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +5821,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +5841,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29738</t>
+          <t>29640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44902</t>
+          <t>45547</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +5856,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>76,38%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6001,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15965</t>
+          <t>16848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>32482</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6016,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6036,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6051,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6071,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40235</t>
+          <t>38053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6086,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>49,77%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6114,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34800</t>
+          <t>34408</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50925</t>
+          <t>50042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6129,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6149,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6164,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6184,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55143</t>
+          <t>55090</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6199,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +6344,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44363</t>
+          <t>44298</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67830</t>
+          <t>68776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +6359,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +6379,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24260</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>40771</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +6394,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +6414,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73310</t>
+          <t>73287</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104620</t>
+          <t>103447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +6429,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +6457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69039</t>
+          <t>68093</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92506</t>
+          <t>92571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +6472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +6492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42933</t>
+          <t>43306</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59817</t>
+          <t>61226</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +6507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +6527,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116326</t>
+          <t>117499</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147636</t>
+          <t>147659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +6542,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +6687,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36622</t>
+          <t>35399</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +6702,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +6722,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28306</t>
+          <t>28145</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +6737,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +6757,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38043</t>
+          <t>37359</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59888</t>
+          <t>59735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +6772,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +6800,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32473</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>49735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +6815,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +6835,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>19179</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32842</t>
+          <t>32513</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +6850,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +6870,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56531</t>
+          <t>56684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78376</t>
+          <t>79060</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +6885,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7010,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7708,107 +7020,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135950</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>117715</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156230</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89846</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>103788</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>209</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>225796</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>202638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>251475</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -7821,107 +7133,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214051</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>193771</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>232286</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>121</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126452</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112510</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142034</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>320</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>340503</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>314824</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>363661</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -7934,462 +7246,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>529</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>135950</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>117870</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>154859</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>38,84%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>33,68%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>44,25%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>89846</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>76669</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>105873</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>41,54%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>35,45%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>48,95%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>225796</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>202214</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>250839</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>35,71%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>44,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>214051</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>195142</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>232131</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>61,16%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>55,75%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>66,32%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>126452</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>110425</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>139629</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>58,46%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>51,05%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>64,55%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>340503</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>315460</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>364085</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>60,13%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>55,71%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>64,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8399,7 +7368,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8412,7 +7380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8443,7 +7411,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2023 (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +7606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +7621,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +7641,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20392</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33574</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +7656,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +7676,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32952</t>
+          <t>32621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52238</t>
+          <t>51910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +7691,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,71%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +7719,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>24554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36869</t>
+          <t>37240</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +7734,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +7754,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25035</t>
+          <t>24988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38217</t>
+          <t>37654</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +7769,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +7789,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52187</t>
+          <t>52515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71473</t>
+          <t>71804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +7804,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,76%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +7949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>18535</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +7964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +7984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16703</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +7999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +8019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>15369</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32583</t>
+          <t>31857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +8034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +8062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31559</t>
+          <t>31384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43684</t>
+          <t>43581</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +8077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +8097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25455</t>
+          <t>24605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35442</t>
+          <t>34984</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +8112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +8132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59495</t>
+          <t>60221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75816</t>
+          <t>76709</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +8147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +8292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>11563</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28968</t>
+          <t>28023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +8307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +8327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>9988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +8342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +8362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>16928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>35624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +8377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +8405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27764</t>
+          <t>28709</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45121</t>
+          <t>45169</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +8420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +8440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +8455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +8475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39569</t>
+          <t>38947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57257</t>
+          <t>57643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +8490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +8635,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37321</t>
+          <t>37669</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61768</t>
+          <t>62372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +8650,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +8670,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33189</t>
+          <t>33018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50238</t>
+          <t>49953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +8685,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +8705,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76217</t>
+          <t>76382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107088</t>
+          <t>106875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +8720,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +8748,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71450</t>
+          <t>70846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95897</t>
+          <t>95549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +8763,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +8783,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55520</t>
+          <t>55805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72569</t>
+          <t>72740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +8798,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +8818,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131888</t>
+          <t>132101</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162759</t>
+          <t>162594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +8833,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +8978,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>13452</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28173</t>
+          <t>28741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +8993,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +9013,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22255</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71448</t>
+          <t>71950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +9028,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +9048,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38253</t>
+          <t>35659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92297</t>
+          <t>91601</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +9063,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +9091,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22997</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37144</t>
+          <t>37718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +9106,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +9126,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55799</t>
+          <t>55297</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104992</t>
+          <t>105809</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +9141,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +9161,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86119</t>
+          <t>86815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140163</t>
+          <t>142757</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +9176,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -10333,7 +9301,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10343,107 +9311,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115185</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96204</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133498</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>194</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136291</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95989</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158735</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>302</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>251476</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>209604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>282100</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -10456,107 +9424,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>227</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>221670</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>203357</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>240651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>276</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215320</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>192876</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>255622</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>503</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>436990</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>406366</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>478862</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -10569,462 +9537,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>335</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>336855</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>336855</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>336855</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>470</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>351611</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>351611</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>351611</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>805</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>688466</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>688466</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>688466</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>115185</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>96638</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>137275</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>34,19%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>28,69%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>40,75%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>136291</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>99642</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>156868</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>38,76%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>28,34%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>44,61%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>251476</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>208444</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>278417</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>36,53%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>40,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>221670</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>199580</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>240217</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>65,81%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>59,25%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>71,31%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>215320</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>194743</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>251969</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>61,24%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>55,39%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>71,66%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>436990</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>410049</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>480022</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>63,47%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>59,56%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>69,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>336855</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>336855</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>336855</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>351611</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>351611</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>351611</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>805</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>688466</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>688466</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>688466</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11034,7 +9659,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
